--- a/backend/master_data/customer_import_template.xlsx
+++ b/backend/master_data/customer_import_template.xlsx
@@ -1,14 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <sheets>
-    <sheet name="Customers" sheetId="1" r:id="rId1"/>
-    <sheet name="Addresses" sheetId="2" r:id="rId2"/>
-    <sheet name="Contacts" sheetId="3" r:id="rId3"/>
-    <sheet name="Banks" sheetId="4" r:id="rId4"/>
-    <sheet name="Identifiers" sheetId="5" r:id="rId5"/>
+    <sheet name="Customers" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Addresses" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Contacts" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Banks" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Identifiers" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Customers'!$A$1:$C$500</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Addresses'!$A$1:$C$500</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Contacts'!$A$1:$G$500</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Banks'!$A$1:$F$500</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Identifiers'!$A$1:$D$500</definedName>
+  </definedNames>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -17,18 +25,18 @@
   <numFmts count="0"/>
   <fonts count="2">
     <font>
+      <name val="Calibri"/>
       <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <b val="1"/>
       <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,38 +55,725 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr" s="2">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>customer_name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr" s="2">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr" s="2">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>country</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>JAMHOOR TEXTILE MILLS LIMITED</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>KOHINOOR TEXTILE MILLS LIMITED</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>KAPILA TEX</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SHAHNIYAL TEXTILES ASSOCIATION</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MONNOOWAL TEXTILE MILLS LIMITED</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>IDREES TEXTILE MILLS LTD.</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>THE SONERI BANK LIMITED</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>OLYMPIA BLENDED FIBRE MILLS LIMITED</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>COMBINE SPINNING PVT LTD</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>I. SUFIA COTTON MILLS LTD</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AHMED TEXTILE</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BASFA TEXTILE PVT LTD.</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AL-ZAMIN TEXTILE MILLS (PVT) LIMITED</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ABDULLAH FIBRES PVT LIMITED</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>FARIHA SPINNING MILLS LTD.</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>FAZAL CLOTH MILLS LIMITED</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ABUL KALAM SPINNING MILLS LTD</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>KHAS TEXTILE MILLS (PRIVATE)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>KHURSHID TRADING COMPANY</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ENGLISH FIBRE &amp; YARN</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -90,26 +785,338 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr" s="2">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>customer_name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr" s="2">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>raw_address</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr" s="2">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>country</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>JAMHOOR TEXTILE MILLS LIMITED</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>MONNOO HOUSE 3-MONTGOMERY ROAD, LAHORE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>KOHINOOR TEXTILE MILLS LIMITED</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>KOHINOOR COLONY, PESHAWAR ROAD, RAWALPINDI</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>KAPILA TEX</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>KOHARA BUDHEWAL ROAD, NEAR LUDHIANA, PUNJAB-141112</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SHAHNIYAL TEXTILES ASSOCIATION</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>8-KM FAISALABAD ROAD, KHARIAN WALA, SHEIKHUPURA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MONNOOWAL TEXTILE MILLS LIMITED</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>MONNOO HOUSE, 03 MONTGOMERY ROAD, LAHORE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>IDREES TEXTILE MILLS LTD.</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>6-C, ISMAIL CENTER, AREA BAHADURABAD, KARACHI</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>OLYMPIA BLENDED FIBRE MILLS LIMITED</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>MONNOO HOUSE, 3-MONTGOMERY ROAD, LAHORE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>COMBINE SPINNING PVT LTD</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>148 AHMED BLOCK, NEW GARDEN TOWN, LAHORE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>I. SUFIA COTTON MILLS LTD</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ADAMJEE COURT 4TH FLOOR, 115-120, MOTIJHEEL C/A, DHAKA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AHMED TEXTILE</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SHOP NO. 5 MEMON MANZIL, ADAMJEE DAWOOD ROAD, KARACHI</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>BASFA TEXTILE PVT LTD.</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>20-KM FEROZPUR ROAD, AL NOOR TOWN, LAHORE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AL-ZAMIN TEXTILE MILLS (PVT) LIMITED</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>5A-Z-H, MADINA TOWN, FAISALABAD</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ABDULLAH FIBRES PVT LIMITED</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>RAFIQUE BARKI MARKET GALI, WAKILAN WALI 4 KATCHERY BAZAR, FAISALABAD</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>FARIHA SPINNING MILLS LTD.</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>IMPETUS CENTER 242/B, TEJGAON GULSHAN LINK ROAD, LEVEL-06, TEJGAON INDUSTRIAL AREA, DHAKA-1208</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>FAZAL CLOTH MILLS LIMITED</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>59/3, ABDALI ROAD, MULTAN</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ABUL KALAM SPINNING MILLS LTD</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CHOTTO SHILMONDI, TRIPURDI, SONARGAON, NARAYANGANJ</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>KHAS TEXTILE MILLS (PRIVATE)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>KHAS HOUSE, K-2/3, 2/4, 2/5, CHOUDHRY KHALIQ-UZ-ZAMAN RD, MAIN GIZRI CLIFTON, KARACHI</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>KHURSHID TRADING COMPANY</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>S-17 BEAUMONT PLAZA CL-10, BEAUMONT ROAD, KARACHI</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
         </is>
       </c>
     </row>
@@ -121,52 +1128,782 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="6" max="6" width="22" style="1" customWidth="1"/>
-    <col min="7" max="7" width="22" style="1" customWidth="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" style="1" min="6" max="6"/>
+    <col width="22" customWidth="1" style="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr" s="2">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>customer_name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr" s="2">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>contact_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr" s="2">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>job_title</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr" s="2">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>contact_type</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr" s="2">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr" s="2">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>phone</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr" s="2">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>fax</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>JAMHOOR TEXTILE MILLS LIMITED</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>MRAFIQ@MONNOO.COM</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr"/>
+      <c r="G2" s="1" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>JAMHOOR TEXTILE MILLS LIMITED</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>IMPEX@MONNOO.COM</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr"/>
+      <c r="G3" s="1" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>JAMHOOR TEXTILE MILLS LIMITED</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>36361737</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>JAMHOOR TEXTILE MILLS LIMITED</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>36364412-15 Ext. 241</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>KOHINOOR TEXTILE MILLS LIMITED</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>KHURSHEED.ANWAW@KMLG.COM</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr"/>
+      <c r="G6" s="1" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>KOHINOOR TEXTILE MILLS LIMITED</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t>(042) 111 941 941</t>
+        </is>
+      </c>
+      <c r="G7" s="1" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>KAPILA TEX</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>+91 9814025312</t>
+        </is>
+      </c>
+      <c r="G8" s="1" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>KAPILA TEX</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>NEELAJAIN64@YAHOO.COM</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="inlineStr"/>
+      <c r="G9" s="1" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SHAHNIYAL TEXTILES ASSOCIATION</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>shahniyaltextilesassociation@gmail.com</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="inlineStr"/>
+      <c r="G10" s="1" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SHAHNIYAL TEXTILES ASSOCIATION</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="inlineStr">
+        <is>
+          <t>+92 563 544 055</t>
+        </is>
+      </c>
+      <c r="G11" s="1" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SHAHNIYAL TEXTILES ASSOCIATION</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Fax</t>
+        </is>
+      </c>
+      <c r="F12" s="1" t="inlineStr"/>
+      <c r="G12" s="1" t="inlineStr">
+        <is>
+          <t>+92 563 544 055</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MONNOOWAL TEXTILE MILLS LIMITED</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="F13" s="1" t="inlineStr">
+        <is>
+          <t>92426361631</t>
+        </is>
+      </c>
+      <c r="G13" s="1" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>MONNOOWAL TEXTILE MILLS LIMITED</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>IMPEX@MONNOO.COM</t>
+        </is>
+      </c>
+      <c r="F14" s="1" t="inlineStr"/>
+      <c r="G14" s="1" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>IDREES TEXTILE MILLS LTD.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>IDREESTEXTILE@GMIAL.COM</t>
+        </is>
+      </c>
+      <c r="F15" s="1" t="inlineStr"/>
+      <c r="G15" s="1" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>IDREES TEXTILE MILLS LTD.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="F16" s="1" t="inlineStr">
+        <is>
+          <t>(92-21) 34940026 to 34940030</t>
+        </is>
+      </c>
+      <c r="G16" s="1" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>THE SONERI BANK LIMITED</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="F17" s="1" t="inlineStr">
+        <is>
+          <t>042-36368142-3</t>
+        </is>
+      </c>
+      <c r="G17" s="1" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>THE SONERI BANK LIMITED</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>cs@soneribank.com</t>
+        </is>
+      </c>
+      <c r="F18" s="1" t="inlineStr"/>
+      <c r="G18" s="1" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>COMBINE SPINNING PVT LTD</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>INFO@COMBINESPINNING.COM</t>
+        </is>
+      </c>
+      <c r="F19" s="1" t="inlineStr"/>
+      <c r="G19" s="1" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>COMBINE SPINNING PVT LTD</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="F20" s="1" t="inlineStr">
+        <is>
+          <t>0092-3591 3181-4</t>
+        </is>
+      </c>
+      <c r="G20" s="1" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>BASFA TEXTILE PVT LTD.</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="F21" s="1" t="inlineStr">
+        <is>
+          <t>42-352-71474</t>
+        </is>
+      </c>
+      <c r="G21" s="1" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>BASFA TEXTILE PVT LTD.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>BASFA@CYBER.NET.PK</t>
+        </is>
+      </c>
+      <c r="F22" s="1" t="inlineStr"/>
+      <c r="G22" s="1" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>AL-ZAMIN TEXTILE MILLS (PVT) LIMITED</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="F23" s="1" t="inlineStr">
+        <is>
+          <t>041-8503551-2</t>
+        </is>
+      </c>
+      <c r="G23" s="1" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AL-ZAMIN TEXTILE MILLS (PVT) LIMITED</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>info@alzamingroup.com</t>
+        </is>
+      </c>
+      <c r="F24" s="1" t="inlineStr"/>
+      <c r="G24" s="1" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AL-ZAMIN TEXTILE MILLS (PVT) LIMITED</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Fax</t>
+        </is>
+      </c>
+      <c r="F25" s="1" t="inlineStr"/>
+      <c r="G25" s="1" t="inlineStr">
+        <is>
+          <t>041-8503553</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ABDULLAH FIBRES PVT LIMITED</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>marketing@abdullahfibres.com</t>
+        </is>
+      </c>
+      <c r="F26" s="1" t="inlineStr"/>
+      <c r="G26" s="1" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ABDULLAH FIBRES PVT LIMITED</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="F27" s="1" t="inlineStr">
+        <is>
+          <t>+92-41-2412893</t>
+        </is>
+      </c>
+      <c r="G27" s="1" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ABDULLAH FIBRES PVT LIMITED</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Fax</t>
+        </is>
+      </c>
+      <c r="F28" s="1" t="inlineStr"/>
+      <c r="G28" s="1" t="inlineStr">
+        <is>
+          <t>+92-41-2620703</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>FARIHA SPINNING MILLS LTD.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="F29" s="1" t="inlineStr">
+        <is>
+          <t>+88 02 8878931-32</t>
+        </is>
+      </c>
+      <c r="G29" s="1" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>FARIHA SPINNING MILLS LTD.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>info@farihagroup.com</t>
+        </is>
+      </c>
+      <c r="F30" s="1" t="inlineStr"/>
+      <c r="G30" s="1" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>FAZAL CLOTH MILLS LIMITED</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="F31" s="1" t="inlineStr">
+        <is>
+          <t>92 61 4573338-9</t>
+        </is>
+      </c>
+      <c r="G31" s="1" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ABUL KALAM SPINNING MILLS LTD</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="F32" s="1" t="inlineStr">
+        <is>
+          <t>880 9611-922922</t>
+        </is>
+      </c>
+      <c r="G32" s="1" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ENGLISH FIBRE &amp; YARN</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Usman Rafiq Moon</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="F33" s="1" t="inlineStr">
+        <is>
+          <t>+92 321 2929000</t>
+        </is>
+      </c>
+      <c r="G33" s="1" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ENGLISH FIBRE &amp; YARN</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Usman Rafiq Moon</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="F34" s="1" t="inlineStr">
+        <is>
+          <t>+92 21 34529045 - 6</t>
+        </is>
+      </c>
+      <c r="G34" s="1" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ENGLISH FIBRE &amp; YARN</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Usman Rafiq Moon</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>usman@englishfibre.com</t>
+        </is>
+      </c>
+      <c r="F35" s="1" t="inlineStr"/>
+      <c r="G35" s="1" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>JAMHOOR TEXTILE MILLS LIMITED</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>hashmi@monnoo.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>JAMHOOR TEXTILE MILLS LIMITED</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Fax</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>36278853-36364431</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>KHAS TEXTILE MILLS (PRIVATE)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>iqbal@khasindustries.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>KHURSHID TRADING COMPANY</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>92 21 567 3334-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>KHURSHID TRADING COMPANY</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>MB@MBTEX.NET</t>
         </is>
       </c>
     </row>
@@ -178,46 +1915,258 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="17" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="5" max="5" width="22" style="1" customWidth="1"/>
-    <col min="6" max="6" width="22" style="1" customWidth="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" style="1" min="5" max="5"/>
+    <col width="22" customWidth="1" style="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr" s="2">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>customer_name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr" s="2">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>bank_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr" s="2">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>branch_name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr" s="2">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>bank_country</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr" s="2">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>swift_bic_code</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr" s="2">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>account_no</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>JAMHOOR TEXTILE MILLS LIMITED</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SONERI BANK LIMITED</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr"/>
+      <c r="F2" s="1" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>KOHINOOR TEXTILE MILLS LIMITED</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>HABIB BANK LIMITED</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr"/>
+      <c r="F3" s="1" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>MONNOOWAL TEXTILE MILLS LIMITED</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BANK ALFALAH LIMITED</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CENTRALIZED IMPORTS, KARACHI, PAKISTAN</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr"/>
+      <c r="F4" s="1" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>IDREES TEXTILE MILLS LTD.</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BANK ALFALAH LIMITED</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CENTRALIZED IMPORTS, KARACHI, PAKISTAN</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr"/>
+      <c r="F5" s="1" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>OLYMPIA BLENDED FIBRE MILLS LIMITED</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SINDH BANK LIMITED</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr"/>
+      <c r="F6" s="1" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>COMBINE SPINNING PVT LTD</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BANK ALFALAH LIMITED</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr"/>
+      <c r="F7" s="1" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BASFA TEXTILE PVT LTD.</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>HABIB BANK LIMITED</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>LAHORE, PAKISTAN</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="inlineStr"/>
+      <c r="F8" s="1" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AL-ZAMIN TEXTILE MILLS (PVT) LIMITED</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>MEEZAN BANK LIMITED</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>FAISALABAD</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr"/>
+      <c r="F9" s="1" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ABDULLAH FIBRES PVT LIMITED</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>MEEZAN BANK LIMITED</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr"/>
+      <c r="F10" s="1" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AHMED TEXTILE</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>HABIB METROPOLITAN BANK LTD.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
         </is>
       </c>
     </row>
@@ -229,33 +2178,236 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="19" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="3" max="3" width="22" style="1" customWidth="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" style="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr" s="2">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>customer_name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr" s="2">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>identifier_type</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr" s="2">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>identifier_value</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr" s="2">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>issuing_country</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>KOHINOOR TEXTILE MILLS LIMITED</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NTN</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>0658187-7</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>KAPILA TEX</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>GSTIN</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>03ANQPJ9251R1Z7</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>KAPILA TEX</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>IEC</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>3017501299</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>KAPILA TEX</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PAN</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>3017501299</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>IDREES TEXTILE MILLS LTD.</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>NTN</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>0804275-6</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>OLYMPIA BLENDED FIBRE MILLS LIMITED</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>NTN</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>0657802-7</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>COMBINE SPINNING PVT LTD</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>NTN</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>2270469-8</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>I. SUFIA COTTON MILLS LTD</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BIN/VAT</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>000291845-0103</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ABDULLAH FIBRES PVT LIMITED</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>NTN</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>2207242-0</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
         </is>
       </c>
     </row>
